--- a/LISTAS/mi/SOPORTE LUQUE.xlsx
+++ b/LISTAS/mi/SOPORTE LUQUE.xlsx
@@ -686,7 +686,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45163.60925780248</v>
+        <v>45217</v>
       </c>
     </row>
     <row r="2">
@@ -722,7 +722,7 @@
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E5" s="7" t="n"/>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="D10" s="15" t="n">
-        <v>52.5</v>
+        <v>49.8</v>
       </c>
       <c r="E10" s="7" t="n"/>
     </row>
@@ -810,7 +810,6 @@
       <c r="D12" s="18" t="n"/>
       <c r="E12" s="7" t="n"/>
     </row>
-    <row r="13"/>
     <row r="14" ht="26.25" customHeight="1" s="25">
       <c r="A14" s="21" t="inlineStr">
         <is>
@@ -859,13 +858,10 @@
           <t>Jgo.</t>
         </is>
       </c>
-      <c r="D16" s="11" t="n"/>
-    </row>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
+      <c r="D16" s="11" t="n">
+        <v>32.2</v>
+      </c>
+    </row>
     <row r="22" ht="15" customHeight="1" s="25">
       <c r="A22" s="9" t="inlineStr">
         <is>

--- a/LISTAS/mi/SOPORTE LUQUE.xlsx
+++ b/LISTAS/mi/SOPORTE LUQUE.xlsx
@@ -686,7 +686,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45217</v>
+        <v>45232</v>
       </c>
     </row>
     <row r="2">
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="D10" s="15" t="n">
-        <v>49.8</v>
+        <v>60</v>
       </c>
       <c r="E10" s="7" t="n"/>
     </row>
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="D16" s="11" t="n">
-        <v>32.2</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="25">
@@ -871,8 +871,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" scale="85" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOPORTE LUQUE.xlsx
+++ b/LISTAS/mi/SOPORTE LUQUE.xlsx
@@ -686,7 +686,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45232</v>
+        <v>45237</v>
       </c>
     </row>
     <row r="2">

--- a/LISTAS/mi/SOPORTE LUQUE.xlsx
+++ b/LISTAS/mi/SOPORTE LUQUE.xlsx
@@ -686,7 +686,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45237</v>
+        <v>45238</v>
       </c>
     </row>
     <row r="2">
@@ -871,8 +871,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A14:D14"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" scale="85" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOPORTE LUQUE.xlsx
+++ b/LISTAS/mi/SOPORTE LUQUE.xlsx
@@ -686,7 +686,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45238</v>
+        <v>45244</v>
       </c>
     </row>
     <row r="2">

--- a/LISTAS/mi/SOPORTE LUQUE.xlsx
+++ b/LISTAS/mi/SOPORTE LUQUE.xlsx
@@ -686,7 +686,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45244</v>
+        <v>45252</v>
       </c>
     </row>
     <row r="2">
@@ -871,8 +871,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" scale="85" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOPORTE LUQUE.xlsx
+++ b/LISTAS/mi/SOPORTE LUQUE.xlsx
@@ -686,7 +686,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45252</v>
+        <v>45253</v>
       </c>
     </row>
     <row r="2">
@@ -871,8 +871,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A14:D14"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" scale="85" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOPORTE LUQUE.xlsx
+++ b/LISTAS/mi/SOPORTE LUQUE.xlsx
@@ -686,7 +686,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
     </row>
     <row r="2">
@@ -871,8 +871,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" scale="85" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOPORTE LUQUE.xlsx
+++ b/LISTAS/mi/SOPORTE LUQUE.xlsx
@@ -871,8 +871,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A14:D14"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" scale="85" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOPORTE LUQUE.xlsx
+++ b/LISTAS/mi/SOPORTE LUQUE.xlsx
@@ -686,7 +686,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45254</v>
+        <v>45256</v>
       </c>
     </row>
     <row r="2">
@@ -871,8 +871,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" scale="85" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOPORTE LUQUE.xlsx
+++ b/LISTAS/mi/SOPORTE LUQUE.xlsx
@@ -686,7 +686,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
     </row>
     <row r="2">

--- a/LISTAS/mi/SOPORTE LUQUE.xlsx
+++ b/LISTAS/mi/SOPORTE LUQUE.xlsx
@@ -686,7 +686,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45266</v>
+        <v>45226.54517871882</v>
       </c>
     </row>
     <row r="2">
@@ -722,7 +722,7 @@
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E5" s="7" t="n"/>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="D10" s="15" t="n">
-        <v>60</v>
+        <v>58.5</v>
       </c>
       <c r="E10" s="7" t="n"/>
     </row>
@@ -810,6 +810,7 @@
       <c r="D12" s="18" t="n"/>
       <c r="E12" s="7" t="n"/>
     </row>
+    <row r="13"/>
     <row r="14" ht="26.25" customHeight="1" s="25">
       <c r="A14" s="21" t="inlineStr">
         <is>
@@ -858,10 +859,13 @@
           <t>Jgo.</t>
         </is>
       </c>
-      <c r="D16" s="11" t="n">
-        <v>16.1</v>
-      </c>
-    </row>
+      <c r="D16" s="11" t="n"/>
+    </row>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22" ht="15" customHeight="1" s="25">
       <c r="A22" s="9" t="inlineStr">
         <is>
@@ -871,8 +875,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A14:D14"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" scale="85" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOPORTE LUQUE.xlsx
+++ b/LISTAS/mi/SOPORTE LUQUE.xlsx
@@ -686,7 +686,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45226.54517871882</v>
+        <v>45286</v>
       </c>
     </row>
     <row r="2">
@@ -722,7 +722,7 @@
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E5" s="7" t="n"/>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="D10" s="15" t="n">
-        <v>58.5</v>
+        <v>60</v>
       </c>
       <c r="E10" s="7" t="n"/>
     </row>
@@ -810,7 +810,6 @@
       <c r="D12" s="18" t="n"/>
       <c r="E12" s="7" t="n"/>
     </row>
-    <row r="13"/>
     <row r="14" ht="26.25" customHeight="1" s="25">
       <c r="A14" s="21" t="inlineStr">
         <is>
@@ -859,13 +858,12 @@
           <t>Jgo.</t>
         </is>
       </c>
-      <c r="D16" s="11" t="n"/>
-    </row>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>********</t>
+        </is>
+      </c>
+    </row>
     <row r="22" ht="15" customHeight="1" s="25">
       <c r="A22" s="9" t="inlineStr">
         <is>
